--- a/www/download/COUNTRY.WAL.EXI382.xlsx
+++ b/www/download/COUNTRY.WAL.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - America</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13370490797546</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.13384417177914</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>122.06</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>87.049</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>90.78</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>90.656</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>92.383</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>93.349</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>94.359</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>96.827</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>99.675</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>102.991</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>102.085</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>104.141</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>105.491</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>112.925</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>114.717</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>116.412</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>122.3</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>125.737</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>125.412</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>122.161</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>118.586</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>136.786</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>123.636</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>128.2</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>114.855</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>112.705</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>111.008</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>74.509</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>24.265</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>56.908</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>56.743</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>57.741</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>59.425</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60.347</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>61.307</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>63.056</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>65.244</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>65.172</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>67.011</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>68.675</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>73.609</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>75.095</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>84.189</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>96.846</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>83.478</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>82.989</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>81.001</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>78.245</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>89.136</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>79.044</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>81.068</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>72.241</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>70.18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>69.276</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>283117.929</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>195899</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>206119</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>208322</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>209441</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>210949</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>214229</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>214001</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>225244</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>228629</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>225987</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>230587</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>233624</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>250088</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>258824</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>273988</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>289255</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>293570</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>292152</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>284495.323</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>276298.231</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>319610.124</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>290597.356</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>302722.838</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>270259.089</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>264511.962</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>259121.477</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>181663.245</t>
+          <t>342641364787.828</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>251123323710.678</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>261999151328.66</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52748</t>
+          <t>274694259986.004</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>272138797859.998</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>277017748837.04</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>281977996112.129</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>287070857067.899</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>296599518744.874</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>303087808576.703</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>298057837109.172</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>303669656306.485</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>309600652976.655</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>78094</t>
+          <t>345924211031.831</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>81880</t>
+          <t>358439234839.86</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>127136</t>
+          <t>358849704004.781</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>175561</t>
+          <t>380492415967.491</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>387945904504.254</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>99268</t>
+          <t>382104741881.935</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>191804.544</t>
+          <t>352080856798.333</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>186635.425</t>
+          <t>341039867614.89</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>216182.202</t>
+          <t>378628981541.783</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>195592.827</t>
+          <t>352382251544.368</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>203285.643</t>
+          <t>354047285810.551</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>180192.818</t>
+          <t>318832074143.995</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>174398.905</t>
+          <t>316170888188.848</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>170788.482</t>
+          <t>306943286314.084</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>72212154900.4568</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>53425475627.1125</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>54717346655.6228</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>57165537589.6792</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>60384894291.3264</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>58885689241.2526</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>67178882241.2556</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>63974720109.7689</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>58698285995.863</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>63024973544.665</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>63655166043.1534</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>63847082698.4342</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>65012549149.0908</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>66363929828.3358</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>75702408553.0241</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>77777349151.961</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>79192448877.2091</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>79628528230.2022</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>84194545729.9195</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>77805373885.8158</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>75845235817.2263</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>84827858363.7189</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>77432848595.0411</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>81664847048.3973</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>72278054992.6167</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>66819373690.9869</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>62723548717.1317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>953414323.958279</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>31430108.0194969</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>27307800.8642268</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28153005.8773951</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>29095432.3743452</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>22723250.1906698</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>23799137.6647039</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>29888623.5260063</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>34088145.5224151</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>31882038.782365</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>26886498.1801147</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>23223834.614366</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>22233911.6867418</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>22477750.3627382</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>23409881.1789789</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>18430512.6827815</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>17982193.9602953</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>16175086.8142816</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>15775691.6016665</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>258057253.586484</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>272214342.100583</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>215449929.854947</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>210259979.790091</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>230959673.594121</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>225337253.689444</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>223296402.693668</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>221373153.819607</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>645332.560947545</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1041275.34129811</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1151772.41156606</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1221197.89740717</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1264674.61900467</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1505272.70464493</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1547113.80418115</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1507817.52738877</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1455012.96339948</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1442994.57322765</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1528001.96858845</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1674035.660853</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1775046.98453271</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1917068.7948715</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2012634.02400981</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2417332.08911698</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2663150.12177971</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2886303.01236256</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2851728.48513298</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2780015.76667249</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>3018492.04983671</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3099020.88582831</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3002673.16583829</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2966293.61150806</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2821936.83146256</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2633418.66460569</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2502285.32547801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1277230.85648278</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1908304.32564622</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2168468.46880519</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2337357.25699543</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2442525.9499648</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2972071.755014</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3037678.8755211</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2997776.67029165</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2845214.39152757</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2841272.95654543</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2995413.23917247</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3264542.9129461</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3448304.87422238</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3871414.10396247</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4019949.46278878</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4641132.31304178</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5123068.13393591</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>5765399.52482108</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>5547006.60878013</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>5290451.04452604</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>5788860.89312727</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5857934.72600596</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>5763948.43158691</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5632345.20659469</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>5404162.44334753</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>5098083.89735219</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4859114.85439294</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.51568790484149</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0395227997148133</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.0515804736176878</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.0772762362765004</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.131289362749934</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0278962386692413</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.108127465043297</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.10584993725979</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0313418692378606</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.00596546929779407</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0163040020365506</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0672844728370374</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.114307944360826</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.176753700421669</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.0816036314447803</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.634614722489363</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.2168906567366</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.261432331257993</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.179031244119071</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.46518376007225</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.46074024954318</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.54848119543075</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.52596708362612</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.48926741290025</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.49305018552409</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.61000508314406</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.72287658516529</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>969.167770033019</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2201.75048947543</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>961.50535347627</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1007.4465148071</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1045.78885525558</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>990.924513946382</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1113.20997300995</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1043.51411926512</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>930.891366338831</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>965.988804252666</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>976.725680401755</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>952.785105407303</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>946.669809233646</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>901.573582419926</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1008.08853522882</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>923.842178336606</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>817.71522703274</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>953.886391986026</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1014.52657255689</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>960.543048364143</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>969.325301817926</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>951.663962552959</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>979.619630567592</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1007.36636236353</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1000.51983996094</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>952.108025196644</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>905.409872366349</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>-38242541623.1622</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>-21668789085.1771</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-26777991563.4541</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>-26029233020.6309</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>-23386585507.214</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>-18253657202.8567</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>-17674569837.0234</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-24167243098.9538</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>-29830932472.2111</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>-24785014341.5374</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>-21013945889.9486</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>-22445789629.3306</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>-29277145262.3319</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>-25081761108.3628</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>-19498988615.4073</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>-17626652776.2525</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>-25884027252.8392</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>-22656067835.8215</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>-30613549449.5804</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>-36175049893.9505</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>-45852177246.6815</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>-39497945742.9804</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.196</t>
+          <t>-36607325641.7493</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>-31296843685.6484</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>-28749819134.9936</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>-30683917445.1014</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>-27481351035.708</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-39827724861.728</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-20106006099.7105</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-25462297345.2686</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-25466268460.3351</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-22809866216.8974</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-17948904052.3048</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-21998968254.1598</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-27766626169.0353</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-30528611110.0079</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-25886486400.16</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-20903723750.177</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-20864555496.2464</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-25566318815.638</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-24127365902.9526</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-20234254012.0607</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-18515185072.7934</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-22578567854.5493</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-18760335530.7647</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-25253743661.555</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-31204934773.2907</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-38710533506.717</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-33380234607.7474</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-37118193937.4459</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-32521504255.1747</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-30380872270.1198</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-32539177537.534</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-26536509920.6403</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1585183238.56581</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1562782985.46667</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1315694218.18556</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-562964560.295839</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-576719290.316649</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-304753150.551871</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4324398417.13643</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3599383070.08152</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>697678637.796793</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1101472058.62259</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-110222139.771534</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-1581234133.0842</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-3710826446.69392</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-954395205.410133</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>735265396.653339</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>888532296.540905</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-3305459398.29</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-3895732305.0568</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-5359805788.02538</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-4970115120.65988</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-7141643739.96451</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-6117711135.233</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>510868295.696571</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1224660569.52629</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1631053135.12622</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1855260092.4326</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-944841115.067745</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>2438.12363683426</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>2288.76983309296</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>911.910451958021</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>929.594839892931</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>908.487902878093</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.874</t>
+          <t>963.281447202132</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>992.841400567463</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.499</t>
+          <t>933.058215211199</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>960.067241817276</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>960.226227698884</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.673</t>
+          <t>992.650217884177</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1016.89274895161</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>1054.8816891156</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.326</t>
+          <t>1060.93004931507</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.349</t>
+          <t>1090.35222052134</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.899</t>
+          <t>1510.12602596566</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.076</t>
+          <t>1812.78524668013</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.665</t>
+          <t>1203.26313519821</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>1196.15852703361</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.692</t>
+          <t>2367.91512367758</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4.342</t>
+          <t>2385.25778508396</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4.062</t>
+          <t>2425.29771293533</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>2474.48694128772</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.989</t>
+          <t>2507.60425868341</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>3.968</t>
+          <t>2494.34617263516</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>2485.0067854655</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.038</t>
+          <t>2465.31934144383</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>2319.49871173881</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2250.44515158096</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>2270.53315708331</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>2297.93946346698</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>2267.09459532638</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>2259.78853549577</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>2270.36106783603</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>2210.13766821216</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>2259.78429897115</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>2219.89300035903</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>2213.71406181113</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>2214.18077414328</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>2214.63442379003</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>2214.63803409361</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>2256.19568154675</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>2353.60615744115</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>2365.12673753082</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>2334.79405425644</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>2329.53784326841</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>2328.85444796391</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>2329.93562388626</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>2336.5770395211</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.196</t>
+          <t>2350.42032294396</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>2361.33355083252</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>2353.03943703384</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>2346.93111718374</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>2334.25335922259</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>149655.226717242</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>180205.267701026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>211594.142353644</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>210075.348512713</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>231162.91033435</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>312676.206278503</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>326361.323330237</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>307131.392042671</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>280806.191592986</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>306041.517191944</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>366954.526034736</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>426364.188649704</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>428238.306209793</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>446165.549868685</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>402264.537122321</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>539762.921951523</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>569163.325176614</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>640116.08521893</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>604739.339207366</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>556365.836074787</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>573150.454538645</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>566436.103924769</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>592710.663537675</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>565508.30522938</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>594867.672920575</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>625490.33310517</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>659171.105592599</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>46731205113.8722</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>31401181899.7986</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>35617827197.8999</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>35530631093.7404</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>39025141190.7262</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>41721908707.3238</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>45465857205.7458</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>51717900593.0626</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>54338091722.41</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>55717931880.0613</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>55227773726.6968</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>56994778851.8256</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>55652912928.4528</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>58595741443.6457</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>55582107743.1553</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>57048978068.6515</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>65740829068.3999</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>68600815844.3474</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>64152701661.4598</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>58390366661.4359</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>55107727827.6817</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>60217605050.6894</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>57872818510.2676</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>58119122274.7957</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>54585038250.4411</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>60641975158.1492</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>58974838369.6693</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>182866.293805159</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>209084.786729003</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>268624.647105682</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>272168.504805724</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>260349.988439034</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>313525.039975135</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>319343.376993824</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>288118.430404088</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>256491.08568257</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>281472.39197069</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>343766.429715646</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>413495.035156365</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>450921.935359427</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>486275.894977807</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>434079.745305235</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>565610.975238962</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>618882.039436985</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>746908.098920531</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>757741.574145555</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>725167.121255796</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>993850.372838792</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>780307.087067634</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>831233.18543324</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>699683.439341904</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>711444.226823678</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>729686.803913413</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>761274.052613463</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>283117.929</t>
+          <t>27303604444.3983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>195899</t>
+          <t>15598921960.7356</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>206119</t>
+          <t>19515245628.9808</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>21199644434.9027</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>209441</t>
+          <t>20992746912.1356</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>210949</t>
+          <t>23599940055.1119</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>214229</t>
+          <t>26659440081.8305</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>214001</t>
+          <t>24369151112.888</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>20376566026.157</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>26427189554.727</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>225987</t>
+          <t>30335605178.1881</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>230587</t>
+          <t>32634166001.8838</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>233624</t>
+          <t>29192675265.7763</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>250088</t>
+          <t>39010675935.138</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>258824</t>
+          <t>40766044479.137</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>273988</t>
+          <t>42609442382.3607</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>289255</t>
+          <t>45590152903.3872</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>57588412781.5769</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>292152</t>
+          <t>51066102423.6328</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>284495.323</t>
+          <t>40159921811.0712</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>276298.231</t>
+          <t>49922459130.8064</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>319610.124</t>
+          <t>43402074019.8826</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>290597.356</t>
+          <t>44240639789.593</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>302722.838</t>
+          <t>40157905741.8853</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>270259.089</t>
+          <t>36474858801.9778</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>264511.962</t>
+          <t>40069421449.3089</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>259121.477</t>
+          <t>41441895531.1199</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>181663.245</t>
+          <t>-33211.0670879164</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>-28879.5190279773</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>-57030.5047520377</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>52748</t>
+          <t>-62093.1562930116</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>-29187.0781046846</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>57243</t>
+          <t>-848.833696632082</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>7017.94633641285</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>19012.9616385833</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>60538</t>
+          <t>24315.1059104166</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>24569.125221254</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>23188.09631909</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>12869.1534933389</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>-22683.629149634</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>78094</t>
+          <t>-40110.3451091221</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>81880</t>
+          <t>-31815.2081829146</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>127136</t>
+          <t>-25848.053287439</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>175561</t>
+          <t>-49718.7142603706</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>-106792.013701601</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>99268</t>
+          <t>-153002.234938189</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>191804.544</t>
+          <t>-168801.285181009</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>186635.425</t>
+          <t>-420699.918300147</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>216182.202</t>
+          <t>-213870.983142865</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>195592.827</t>
+          <t>-238522.521895565</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>203285.643</t>
+          <t>-134175.134112523</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>180192.818</t>
+          <t>-116576.553903104</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>174398.905</t>
+          <t>-104196.470808243</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>170788.482</t>
+          <t>-102102.947020864</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>270257.73</t>
+          <t>19427600669.4739</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>201291.585</t>
+          <t>15802259939.0631</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>209379.826</t>
+          <t>16102581568.9191</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>218380.146</t>
+          <t>14330986658.8377</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>216200.694</t>
+          <t>18032394278.5906</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>219326.745</t>
+          <t>18121968652.2119</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>223383.247</t>
+          <t>18806417123.9153</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>226871.154</t>
+          <t>27348749480.1746</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>235054.06</t>
+          <t>33961525696.253</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>240335.961</t>
+          <t>29290742325.3344</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>237014.239</t>
+          <t>24892168548.5087</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>241897.922</t>
+          <t>24360612849.9418</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>246474.882</t>
+          <t>26460237662.6764</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>274042.595</t>
+          <t>19585065508.5078</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>283981.531</t>
+          <t>14816063264.0183</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>286445.77</t>
+          <t>14439535686.2908</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>303414.704</t>
+          <t>20150676165.0127</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>307758.096</t>
+          <t>11012403062.7705</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>304519.656</t>
+          <t>13086599237.827</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>281527.038</t>
+          <t>18230444850.3646</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>273251.554</t>
+          <t>5185268696.87532</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>302769.376</t>
+          <t>16815531030.8068</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>281742.734</t>
+          <t>13632178720.6746</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>283334.297</t>
+          <t>17961216532.9104</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>254893.742</t>
+          <t>18110179448.4633</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>252371.605</t>
+          <t>20572553708.8403</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>244525.493</t>
+          <t>17532942838.5494</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>322871.037689392</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>326860.331859745</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>399503.890244024</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>405210.099273659</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>403728.525958011</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>483344.727273626</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>497528.058747419</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.062</t>
+          <t>388334.722177755</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>344477.480411154</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>373074.827586959</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.078</t>
+          <t>446034.503174205</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>514439.34132976</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.391</t>
+          <t>550157.152233751</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>612409.41852844</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>623514.137555414</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>3.229</t>
+          <t>792036.703816295</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>3.564</t>
+          <t>818576.413671073</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>976977.550173298</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.838</t>
+          <t>958046.040014793</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3.645</t>
+          <t>942711.083668923</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1095483.48658984</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>1045868.68130445</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>1083325.76050577</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>997010.12805205</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>3.607</t>
+          <t>989144.157784109</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3.402</t>
+          <t>991308.433155069</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3.234</t>
+          <t>1026991.71524878</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>173122.68</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>137026.637</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>139159.687</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>143519.375</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>140906.192</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>140301.88</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>143613.617</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>144390.499</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>151677.9</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>153928.915</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>152043.45</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>155719.758</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>159369.814</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>171296.713</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>179456.734</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>186906.739</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>197793.275</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>194215.41</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>196440.901</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>185010.753</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>177828.79</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>200305.94</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>183570.124</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>186460.198</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>166487.218</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>163318.285</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>158065.76</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>353936.583233514</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>378743.314827232</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>453047.944596949</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>494673.444672901</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>503833.623992683</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>596388.866629703</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>612242.588510416</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>452975.752793312</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>390713.551143525</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>413496.633661557</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>492488.844457846</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>561999.364340558</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>597073.873878336</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>664545.503666832</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>696482.235981962</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>842971.188999391</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>930047.963937269</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>1114771.12824581</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>1137853.97207971</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2.395</t>
+          <t>1129958.77823642</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2.571</t>
+          <t>1356187.79327453</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>1280801.63162372</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>1361947.05194541</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2.494</t>
+          <t>1239975.09060905</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>1228488.39546359</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>1187340.00050766</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2.091</t>
+          <t>1224841.12521708</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>66679.442</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>49860.05</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>50835.783</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>53210.463</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>55524.793</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>54402.325</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>61949.464</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>58995.844</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>54046.652</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>58429.708</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>59367.62</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>59567.916</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>61150.713</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>61520.584</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>70068.886</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>72540.25</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>73993.219</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>73957.965</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>78664.382</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>72672.688</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>71304.273</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>79442.952</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>73165.431</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>76476.471</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>67895.448</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>62538.264</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>59022.078</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>172.44</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>11.39</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-5.53</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>5.22</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-3.28</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-3.04</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>12.01</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>7.22</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>18.47</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>26.94</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>75.26</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>137.27</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>35.81</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>26.19</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>163.93</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>161.75</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>172.12</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>167.33</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>165.81</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>165.4</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>178.87</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>189.36</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1062.434</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>32.382</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>28.119</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>28.842</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>29.819</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>23.248</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24.332</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>30.509</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>34.879</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>32.595</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>27.647</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>23.837</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>22.808</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>23.031</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>23.944</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>18.952</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>18.453</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>16.158</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>287.664</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>303.75</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>239.933</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>234.258</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>257.358</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>251.164</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>248.825</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>246.717</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>204842.373293512</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>218241.740769548</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>273236.610315479</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>261500.065106642</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>266233.735642921</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>333550.250990858</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>333993.346219016</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>247443.935535451</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>219833.645660091</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>234345.797980387</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>282654.612624366</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>328588.745658994</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>361708.048765275</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>394372.950646352</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>407872.580064163</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>526265.147302633</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>520973.951309099</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>627895.414915593</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>628681.76776493</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>611297.491687551</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>695026.312137591</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>677836.418731351</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>712058.797973974</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>657228.332848245</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>654625.617379243</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>695407.716862779</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>711855.434913914</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>181663244665.619</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>55536999999.9915</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>51895000000.0226</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>52748000000.026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52457000000.096</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>57242999999.9758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>59915000000.0665</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>57202999999.9373</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>60538000000.0319</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>62648999999.9901</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>64692999999.9579</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>68142999999.981</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>72443999999.9806</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>78094000000.0182</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>81880000000.0672</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>127135999999.991</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>175560999999.976</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>100446000000.067</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>99267999999.987</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>191804544149.663</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>186635424511.543</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>216182201888.601</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>195592826742.479</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>203285642537.059</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>180192818408.664</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>174398904985.979</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>170788482140.352</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>283117928660.332</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>195898999999.973</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>206119000000.008</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>208322000000.006</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>209441000000.063</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>210949000000.003</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>214229000000.011</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>214000999999.968</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>225243999999.979</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>228628999999.995</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>225986999999.999</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>230587000000.011</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>233623999999.988</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>250087999999.998</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>258824000000.031</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>273988000000.003</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>289255000000.004</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>293570000000.022</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>292151999999.982</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>284495322784.564</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>276298230970.686</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>319610123782.832</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>290597356244.036</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>302722838437.698</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>270259088722.965</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>264511962122.899</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>259121477325.377</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>173122680447.92</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>137026637256.195</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>139159687445.371</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>143519375020.976</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>140906192011.979</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>140301880438.488</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>143613616888.841</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>144390499191.984</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>151677900265.414</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>153928914847.872</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>152043449598.243</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>155719758426.231</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>159369813726.084</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>171296712919.681</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>179456733537.71</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>186906738733.41</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>197793274933.781</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>194215410048.117</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>196440901116.707</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>185010753299.696</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>177828790167.523</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>200305940004.544</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>183570124436.149</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>186460197937.079</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>166487218419.219</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>163318284854.807</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>158065759734.688</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>122059963.744534</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>87049000.0000008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>90779999.9999937</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>90655999.9999751</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>92383000.0000113</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>93349000.0000037</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>94359000.0000313</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96826999.9999953</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>99675000.0000131</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>102991000.000009</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>102085000.000004</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>104140999.99998</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>105490999.999979</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>112924999.999989</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>114717000.000015</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>116411999.999984</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>122299999.999994</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>125736999.999992</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>125412000.000002</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>122161057.782419</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>118586208.193096</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>136785613.475145</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>123636335.768257</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>128199948.004368</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>114855316.264331</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>112705464.675208</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>111008291.495691</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>74509447.3147788</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24264999.999996</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>56907999.9999951</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>56742999.99998</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>57741000.0000133</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>59424999.9999887</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60347000.0000219</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>61306999.9999832</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>63056000.0000018</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>65244000.0000042</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>65172000.0000104</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>67010999.9999847</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>68674999.9999685</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>73608999.9999862</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>75095000.0000155</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>84188999.9999789</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>96845999.9999956</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>83477999.9999924</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>82988999.9999959</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>81001443.9418646</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>78245389.5250459</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>89136356.6359679</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>79043790.2415006</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>81067673.1916988</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>72240501.4931422</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>70180454.2369931</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>69276413.5133622</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>283117928660.332</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>195898999999.973</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>206119000000.008</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>208322000000.006</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>209441000000.063</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>210949000000.003</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>214229000000.011</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>214000999999.968</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>225243999999.979</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>228628999999.995</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>225986999999.999</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>230587000000.011</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>233623999999.988</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>250087999999.998</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>258824000000.031</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>273988000000.003</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>289255000000.004</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>293570000000.022</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>292151999999.982</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>284495322784.564</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>276298230970.686</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>319610123782.832</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>290597356244.036</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>302722838437.698</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>270259088722.965</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>264511962122.899</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>259121477325.377</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>181663244665.619</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>55536999999.9915</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>51895000000.0226</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>52748000000.026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52457000000.096</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>57242999999.9758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>59915000000.0665</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>57202999999.9373</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>60538000000.0319</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>62648999999.9901</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>64692999999.9579</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>68142999999.981</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>72443999999.9806</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>78094000000.0182</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>81880000000.0672</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>127135999999.991</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>175560999999.976</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>100446000000.067</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>99267999999.987</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>191804544149.663</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>186635424511.543</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>216182201888.601</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>195592826742.479</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>203285642537.059</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>180192818408.664</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>174398904985.979</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>170788482140.352</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1316886.09984971</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1358327.59724716</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1698870.0675151</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1744610.15482543</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1774347.75289849</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2130510.13005431</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2210534.6653118</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1704019.81565892</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1497777.54205334</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1597956.74312613</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1901492.74737248</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2187211.03523995</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2369959.07300123</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2644158.49101929</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2670539.05873407</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3294527.49299801</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3495627.31699808</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4166569.49517246</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4178034.51261552</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4197378.09295626</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>4938674.79967723</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>4618938.85609387</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>4912335.81268077</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>4536172.42262659</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>4512592.81420635</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>4530757.10650853</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>4592320.20272923</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>519779.987636167</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>555233.317008705</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>672165.473937716</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>707259.181564844</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>716704.380747777</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>839429.411798469</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>878004.589099607</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>656648.029606541</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>572800.250638421</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>609623.871750875</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>726237.843815244</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>832968.919350023</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>896650.670127539</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>997707.145048706</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1031919.80267916</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1274154.16896441</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1357024.58922399</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1625504.52250924</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1634975.555172</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1621988.63354295</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1942825.98910646</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1835725.89813493</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1925805.46044705</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1761404.79200587</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1744410.75190423</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1737303.87361693</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1776364.97616706</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
